--- a/光伏配储项目/电价数据/2026/云路站.xlsx
+++ b/光伏配储项目/电价数据/2026/云路站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.35829</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.94599</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.41056</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18072</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26647</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.6774</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.75547</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.47304</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.62021</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5986699999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7721699999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14247</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.66807</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.69113</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9291799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5628099999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21242</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41195</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.10389</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.11153</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34774</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.43178</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46909</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7416200000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.23455</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.88367</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.02811</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8301499999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.81487</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.54098</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.45593</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.84072</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03116</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.22098</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.60409</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.62722</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.6152000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.61549</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.59113</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.56336</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.21994</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.56443</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5604</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.7161000000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9525800000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.42678</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.85837</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5648099999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.4749</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.74338</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.10094</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.66879</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.88618</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.96974</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.26361</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.75782</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18268</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.95663</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.27836</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.16149</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.34997</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.07177</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.1461</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70721</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04865</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9952000000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02176</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.89479</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.13412</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.98138</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47683</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.92522</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.03089</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44908</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.34003</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.59554</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.56525</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.58585</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5172599999999999</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.56523</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.49068</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.50566</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.13544</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27495</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.02487</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.80903</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7934099999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.01635</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.00855</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.9923500000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.98653</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.6911</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.9235599999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.88664</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8705900000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.11433</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5948300000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6841499999999999</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.90699</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.91284</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8141699999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56577</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.00418</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.53138</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51973</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.61829</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6686299999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6795099999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.67265</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.52569</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6745</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69757</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48268</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6749299999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.87137</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8161499999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.01488</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48477</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.67477</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47683</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5731799999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.69037</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8898400000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6172000000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.05832</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.82112</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6534500000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.5937100000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7375</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.48013</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34825</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.59489</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5699299999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.42495</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.51309</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.54187</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7200599999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.7069</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.40507</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.73092</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.6074299999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48731</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.43575</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.5458200000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.57723</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.80823</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.60389</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.61595</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.51276</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.54432</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.65063</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7838200000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.56514</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6573300000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.60248</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.57409</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5027200000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.38545</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28692</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02249</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44084</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11072</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.05145</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31558</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.23868</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18465</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.20231</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24426</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20905</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18642</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16697</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24481</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26673</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26475</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03661</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009820000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20584</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04908</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05819</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31482</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.51436</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5037</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.49459</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78991</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87027</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6503099999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.48908</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44333</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62807</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.66147</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.02192</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.52398</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43298</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6848099999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9301699999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26423</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6974400000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.54348</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1729</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2595</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25852</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3221</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.85768</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.6101799999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.52751</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.48172</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.26355</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.43617</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5068</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.54963</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.43272</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.56225</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.4685299999999999</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.43604</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.41965</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.4069700000000001</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43865</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4188</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.46169</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.58413</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.45233</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.58401</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.50283</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.45372</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.4278</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.15178</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.65634</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.9997699999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.33258</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.93668</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.68401</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.77552</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.8182</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.65419</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.66365</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.5558500000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.5511699999999999</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.52843</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.59076</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.67237</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.58439</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.52623</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54748</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22099</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.4574</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.19684</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.05529</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.41616</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.42061</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.4506</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5481699999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7744099999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.42881</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5135700000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3383</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.22282</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18009</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.21838</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.18361</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.21518</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.17714</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.24672</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.21588</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.19043</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27063</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28891</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2779</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29468</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30147</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.14617</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6877300000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48397</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44583</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50966</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5696599999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.74091</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45484</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.47947</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.71472</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49597</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7369600000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48584</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24696</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2163</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27522</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.1892</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18183</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27172</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27061</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18353</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18097</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14264</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22972</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25807</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18649</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.23449</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.1927</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15492</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14679</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.21203</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23493</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25941</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30139</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24945</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.2839100000000001</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.26808</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22992</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.22983</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.17555</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22697</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31807</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.04083</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27756</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27938</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27059</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27026</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26796</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29764</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.61763</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.52003</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19338</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29361</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27843</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48962</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64923</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60782</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65464</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80622</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49686</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41052</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27098</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27823</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45059</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4863</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57062</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6831499999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.81921</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.51567</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7276</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6405700000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30587</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39252</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.02754</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.49366</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43022</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.24204</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.24708</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.26923</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.19108</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.19892</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.20734</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.19912</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.23583</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.18965</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21263</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15465</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.0289</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25769</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.03073</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.02998</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1549</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.04248</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19032</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15367</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.02967</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18634</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.14946</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15201</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.02969</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15457</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.02975</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16483</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13777</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22615</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00231</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24278</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29809</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20898</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23631</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25302</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.17455</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18114</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16501</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.17054</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.24862</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22254</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.2775899999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17513</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.1723</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21203</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20303</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18361</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15957</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00034</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01029</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01262</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.005809999999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0342</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00204</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03451</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21382</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25955</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26086</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28704</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.26334</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14606</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.14235</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14635</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14042</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.13046</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16821</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26654</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21573</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.2328</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85449</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86305</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24061</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.6283300000000001</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00287</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06992</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47575</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7456900000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.94477</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58956</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8058200000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8082</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.90408</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29936</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.46464</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25231</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24808</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24796</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23536</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22647</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18425</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14479</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18013</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13986</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.14229</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.13013</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15807</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.21188</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.2547</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22317</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26762</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25878</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28324</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.56352</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47331</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.11488</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8118200000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.80091</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5367799999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6551699999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.85782</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5332100000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41897</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19481</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31019</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28507</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50366</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.02905</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.79832</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53311</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.67843</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55392</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49775</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.65559</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6131799999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98499</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.82797</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.70968</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.57726</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31484</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28425</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27547</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42012</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52543</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19755</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.49124</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.5112599999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.45775</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.55332</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42629</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44885</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.53665</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31833</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.68796</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42131</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26248</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.46989</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.50364</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.46058</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.51962</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.41876</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44333</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33385</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14583</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19875</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14748</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12211</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14598</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18678</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22695</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16438</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17472</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20713</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16424</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.49019</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.6645399999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.43948</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.45951</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53164</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.5714400000000001</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.51815</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.49093</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.48025</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41384</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3652</v>
       </c>
     </row>
   </sheetData>
